--- a/Table_S10.xlsx
+++ b/Table_S10.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S10A_class_signal" sheetId="1" r:id="R92c4f4f88a1242bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S10B_window_signal" sheetId="2" r:id="R343dd1438e7148ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S10A_class_signal" sheetId="1" r:id="R4b2f2a68862d45c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S10B_window_signal" sheetId="2" r:id="R7ea901b091d24744"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -221,9 +221,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -332,12 +332,12 @@
     <x:col min="3" max="3" width="18" style="14" customWidth="1"/>
     <x:col min="4" max="4" width="18" style="14" customWidth="1"/>
     <x:col min="5" max="5" width="18" style="14" customWidth="1"/>
-    <x:col min="6" max="6" width="18" style="14" customWidth="1"/>
+    <x:col min="6" max="6" width="27" style="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" style="14" customWidth="1"/>
     <x:col min="8" max="8" width="18" style="14" customWidth="1"/>
     <x:col min="9" max="9" width="18" style="14" customWidth="1"/>
     <x:col min="10" max="10" width="18" style="14" customWidth="1"/>
-    <x:col min="11" max="11" width="18" style="14" customWidth="1"/>
+    <x:col min="11" max="11" width="24" style="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="14" customFormat="1" ht="36" customHeight="1">
@@ -355,7 +355,7 @@
       <x:c r="J1" s="1" t="n"/>
       <x:c r="K1" s="1" t="n"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Locus class</x:t>
@@ -381,35 +381,31 @@
           <x:t xml:space="preserve">Median HS signal</x:t>
         </x:is>
       </x:c>
-      <x:c r="F2" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">log2FC HS vs NS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" s="10" t="inlineStr">
+      <x:c r="F2" s="21" t="str">
+        <x:v>log2FC HS vs NS [pseudocount 0.05 CPM]</x:v>
+      </x:c>
+      <x:c r="G2" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Welch P</x:t>
         </x:is>
       </x:c>
-      <x:c r="H2" s="10" t="inlineStr">
+      <x:c r="H2" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Wilcoxon P</x:t>
         </x:is>
       </x:c>
-      <x:c r="I2" s="10" t="inlineStr">
+      <x:c r="I2" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Welch BH-adjusted P</x:t>
         </x:is>
       </x:c>
-      <x:c r="J2" s="10" t="inlineStr">
+      <x:c r="J2" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Wilcoxon BH-adjusted P</x:t>
         </x:is>
       </x:c>
-      <x:c r="K2" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Fold label</x:t>
-        </x:is>
+      <x:c r="K2" s="21" t="str">
+        <x:v>Fold label [2^(log2FC)]</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -431,7 +427,7 @@
         <x:v>54.29</x:v>
       </x:c>
       <x:c r="F3" s="12" t="n">
-        <x:v>8.266999999999999</x:v>
+        <x:v>7.965</x:v>
       </x:c>
       <x:c r="G3" s="12" t="n">
         <x:v>0.000757</x:v>
@@ -445,10 +441,8 @@
       <x:c r="J3" s="12" t="n">
         <x:v>0.0809</x:v>
       </x:c>
-      <x:c r="K3" s="12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HS/NS = 308x</x:t>
-        </x:is>
+      <x:c r="K3" s="12" t="str">
+        <x:v>2^(log2FC) = 250×</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -467,7 +461,7 @@
     <x:col min="2" max="2" width="18" style="14" customWidth="1"/>
     <x:col min="3" max="3" width="18" style="14" customWidth="1"/>
     <x:col min="4" max="4" width="18" style="14" customWidth="1"/>
-    <x:col min="5" max="5" width="18" style="14" customWidth="1"/>
+    <x:col min="5" max="5" width="27" style="14" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="18" style="14" customWidth="1"/>
     <x:col min="7" max="7" width="18" style="14" customWidth="1"/>
   </x:cols>
@@ -483,7 +477,7 @@
       <x:c r="F1" s="1" t="n"/>
       <x:c r="G1" s="1" t="n"/>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="10" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Candidate window</x:t>
@@ -504,17 +498,15 @@
           <x:t xml:space="preserve">Mean HS</x:t>
         </x:is>
       </x:c>
-      <x:c r="E2" s="10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">log2FC HS vs NS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="10" t="inlineStr">
+      <x:c r="E2" s="21" t="str">
+        <x:v>log2FC HS vs NS [pseudocount 0.05 CPM]</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Welch BH-adjusted P</x:t>
         </x:is>
       </x:c>
-      <x:c r="G2" s="10" t="inlineStr">
+      <x:c r="G2" s="21" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Wilcoxon BH-adjusted P</x:t>
         </x:is>
